--- a/РАБОЧИЙ СТОЛ/расчет ПОКОМ КИ/Мелитополь/дв 21,07,26 млрсч пок ки.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчет ПОКОМ КИ/Мелитополь/дв 21,07,26 млрсч пок ки.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\07,26\21,07,26 ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\расчет ПОКОМ КИ\Мелитополь\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18B9E98A-D83F-42EA-A237-92AEC6BACC23}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49B0CD8C-3A1D-47F8-B8FE-6A416FA175CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,20 +20,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AN$133</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="338">
   <si>
     <t>дн</t>
   </si>
@@ -1193,7 +1185,7 @@
     <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -1893,7 +1885,7 @@
       </c>
       <c r="W5" s="4">
         <f t="shared" ref="W5:X5" si="1">SUM(W6:W500)</f>
-        <v>-4701.7999999999993</v>
+        <v>-4605.7999999999993</v>
       </c>
       <c r="X5" s="4">
         <f t="shared" si="1"/>
@@ -1905,7 +1897,7 @@
       </c>
       <c r="Z5" s="4">
         <f t="shared" ref="Z5" si="2">SUM(Z6:Z500)</f>
-        <v>-4224</v>
+        <v>-3564</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
@@ -5351,12 +5343,10 @@
       <c r="Y34" s="5">
         <v>500</v>
       </c>
-      <c r="Z34" s="5">
-        <v>-503.99999999999994</v>
-      </c>
+      <c r="Z34" s="5"/>
       <c r="AA34" s="1">
         <f t="shared" si="10"/>
-        <v>7.393073047858941</v>
+        <v>9.5089420654911834</v>
       </c>
       <c r="AB34" s="1">
         <f t="shared" si="7"/>
@@ -5586,19 +5576,15 @@
         <f t="shared" si="6"/>
         <v>93.620000000000061</v>
       </c>
-      <c r="W36" s="5">
-        <v>-95.999999999999986</v>
-      </c>
+      <c r="W36" s="5"/>
       <c r="X36" s="5"/>
       <c r="Y36" s="5">
         <v>100</v>
       </c>
-      <c r="Z36" s="5">
-        <v>-101.99999999999999</v>
-      </c>
+      <c r="Z36" s="5"/>
       <c r="AA36" s="1">
         <f t="shared" si="10"/>
-        <v>8.1875</v>
+        <v>11</v>
       </c>
       <c r="AB36" s="1">
         <f t="shared" si="7"/>
@@ -7586,12 +7572,10 @@
       <c r="Y53" s="5">
         <v>50</v>
       </c>
-      <c r="Z53" s="5">
-        <v>-54</v>
-      </c>
+      <c r="Z53" s="5"/>
       <c r="AA53" s="1">
         <f t="shared" si="10"/>
-        <v>4.741007194244605</v>
+        <v>6.6834532374100721</v>
       </c>
       <c r="AB53" s="1">
         <f t="shared" si="17"/>
@@ -32363,13 +32347,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8FEDC80-15C3-4269-A27B-A4DD4AF59CFE}">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="108.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="94.5703125" customWidth="1"/>
+    <col min="7" max="7" width="84.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>66</v>
       </c>
@@ -32386,8 +32371,17 @@
         <f>D1/C1</f>
         <v>-870</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1" t="s">
+        <v>312</v>
+      </c>
+      <c r="H1">
+        <v>-870</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>49</v>
       </c>
@@ -32404,8 +32398,17 @@
         <f t="shared" ref="E2:E23" si="0">D2/C2</f>
         <v>-396.9</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2" t="s">
+        <v>313</v>
+      </c>
+      <c r="H2">
+        <v>-396.9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>47</v>
       </c>
@@ -32422,8 +32425,17 @@
         <f t="shared" si="0"/>
         <v>-299.7</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" t="s">
+        <v>314</v>
+      </c>
+      <c r="H3">
+        <v>-299.7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>91</v>
       </c>
@@ -32440,8 +32452,17 @@
         <f t="shared" si="0"/>
         <v>-273</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G4" t="s">
+        <v>315</v>
+      </c>
+      <c r="H4">
+        <v>-273</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>89</v>
       </c>
@@ -32458,8 +32479,17 @@
         <f t="shared" si="0"/>
         <v>-270</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G5" t="s">
+        <v>317</v>
+      </c>
+      <c r="H5">
+        <v>-270</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>105</v>
       </c>
@@ -32476,8 +32506,17 @@
         <f t="shared" si="0"/>
         <v>-510</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6" t="s">
+        <v>105</v>
+      </c>
+      <c r="G6" t="s">
+        <v>319</v>
+      </c>
+      <c r="H6">
+        <v>-204</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>178</v>
       </c>
@@ -32494,8 +32533,17 @@
         <f t="shared" si="0"/>
         <v>-195</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7" t="s">
+        <v>178</v>
+      </c>
+      <c r="G7" t="s">
+        <v>318</v>
+      </c>
+      <c r="H7">
+        <v>-195</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>87</v>
       </c>
@@ -32512,8 +32560,17 @@
         <f t="shared" si="0"/>
         <v>-168</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G8" t="s">
+        <v>332</v>
+      </c>
+      <c r="H8">
+        <v>-168</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>93</v>
       </c>
@@ -32530,8 +32587,17 @@
         <f t="shared" si="0"/>
         <v>-162</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9" t="s">
+        <v>93</v>
+      </c>
+      <c r="G9" t="s">
+        <v>316</v>
+      </c>
+      <c r="H9">
+        <v>-162</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>129</v>
       </c>
@@ -32548,8 +32614,17 @@
         <f t="shared" si="0"/>
         <v>-282</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10" t="s">
+        <v>129</v>
+      </c>
+      <c r="G10" t="s">
+        <v>321</v>
+      </c>
+      <c r="H10">
+        <v>-98.7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>97</v>
       </c>
@@ -32566,8 +32641,17 @@
         <f t="shared" si="0"/>
         <v>-67.2</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11" t="s">
+        <v>97</v>
+      </c>
+      <c r="G11" t="s">
+        <v>333</v>
+      </c>
+      <c r="H11">
+        <v>-67.2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>57</v>
       </c>
@@ -32584,8 +32668,17 @@
         <f t="shared" si="0"/>
         <v>-144</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F12" t="s">
+        <v>57</v>
+      </c>
+      <c r="G12" t="s">
+        <v>322</v>
+      </c>
+      <c r="H12">
+        <v>-64.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>55</v>
       </c>
@@ -32602,8 +32695,17 @@
         <f t="shared" si="0"/>
         <v>-138</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F13" t="s">
+        <v>55</v>
+      </c>
+      <c r="G13" t="s">
+        <v>320</v>
+      </c>
+      <c r="H13">
+        <v>-62.1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>166</v>
       </c>
@@ -32620,8 +32722,17 @@
         <f t="shared" si="0"/>
         <v>-150</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F14" t="s">
+        <v>166</v>
+      </c>
+      <c r="G14" t="s">
+        <v>324</v>
+      </c>
+      <c r="H14">
+        <v>-60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>143</v>
       </c>
@@ -32638,8 +32749,17 @@
         <f t="shared" si="0"/>
         <v>-120</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F15" t="s">
+        <v>143</v>
+      </c>
+      <c r="G15" t="s">
+        <v>326</v>
+      </c>
+      <c r="H15">
+        <v>-48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>164</v>
       </c>
@@ -32656,8 +32776,17 @@
         <f t="shared" si="0"/>
         <v>-120</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F16" t="s">
+        <v>164</v>
+      </c>
+      <c r="G16" t="s">
+        <v>327</v>
+      </c>
+      <c r="H16">
+        <v>-48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>184</v>
       </c>
@@ -32674,8 +32803,17 @@
         <f t="shared" si="0"/>
         <v>-128</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F17" t="s">
+        <v>184</v>
+      </c>
+      <c r="G17" t="s">
+        <v>334</v>
+      </c>
+      <c r="H17">
+        <v>-42.24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>123</v>
       </c>
@@ -32692,8 +32830,17 @@
         <f t="shared" si="0"/>
         <v>-101.99999999999999</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F18" t="s">
+        <v>123</v>
+      </c>
+      <c r="G18" t="s">
+        <v>328</v>
+      </c>
+      <c r="H18">
+        <v>-40.799999999999997</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>109</v>
       </c>
@@ -32711,7 +32858,7 @@
         <v>-95.999999999999986</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>111</v>
       </c>
@@ -32728,8 +32875,17 @@
         <f t="shared" si="0"/>
         <v>-90</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G20" t="s">
+        <v>335</v>
+      </c>
+      <c r="H20">
+        <v>-36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>145</v>
       </c>
@@ -32746,8 +32902,17 @@
         <f t="shared" si="0"/>
         <v>-60</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F21" t="s">
+        <v>145</v>
+      </c>
+      <c r="G21" t="s">
+        <v>325</v>
+      </c>
+      <c r="H21">
+        <v>-24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>95</v>
       </c>
@@ -32764,8 +32929,17 @@
         <f t="shared" si="0"/>
         <v>-18</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F22" t="s">
+        <v>95</v>
+      </c>
+      <c r="G22" t="s">
+        <v>336</v>
+      </c>
+      <c r="H22">
+        <v>-18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>190</v>
       </c>
@@ -32781,6 +32955,15 @@
       <c r="E23">
         <f t="shared" si="0"/>
         <v>-41.999999999999993</v>
+      </c>
+      <c r="F23" t="s">
+        <v>190</v>
+      </c>
+      <c r="G23" t="s">
+        <v>337</v>
+      </c>
+      <c r="H23">
+        <v>-13.86</v>
       </c>
     </row>
   </sheetData>
@@ -32790,13 +32973,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B86FF24C-2DE4-46F8-83DA-F0020B93729F}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="108.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="86.7109375" customWidth="1"/>
+    <col min="7" max="7" width="90.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>66</v>
       </c>
@@ -32813,8 +32997,20 @@
         <f>D1/C1</f>
         <v>-1005</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1" t="s">
+        <v>312</v>
+      </c>
+      <c r="H1">
+        <v>1005</v>
+      </c>
+      <c r="J1">
+        <v>-1005</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>49</v>
       </c>
@@ -32831,8 +33027,20 @@
         <f t="shared" ref="E2:E17" si="0">D2/C2</f>
         <v>-405</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2" t="s">
+        <v>313</v>
+      </c>
+      <c r="H2">
+        <v>405</v>
+      </c>
+      <c r="J2">
+        <v>-405</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>47</v>
       </c>
@@ -32849,8 +33057,20 @@
         <f t="shared" si="0"/>
         <v>-405</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" t="s">
+        <v>314</v>
+      </c>
+      <c r="H3">
+        <v>405</v>
+      </c>
+      <c r="J3">
+        <v>-405</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>91</v>
       </c>
@@ -32867,8 +33087,20 @@
         <f t="shared" si="0"/>
         <v>-304.2</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G4" t="s">
+        <v>315</v>
+      </c>
+      <c r="H4">
+        <v>304.2</v>
+      </c>
+      <c r="J4">
+        <v>-304.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>93</v>
       </c>
@@ -32885,8 +33117,20 @@
         <f t="shared" si="0"/>
         <v>-207</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" t="s">
+        <v>93</v>
+      </c>
+      <c r="G5" t="s">
+        <v>316</v>
+      </c>
+      <c r="H5">
+        <v>207</v>
+      </c>
+      <c r="J5">
+        <v>-207</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>89</v>
       </c>
@@ -32903,8 +33147,20 @@
         <f t="shared" si="0"/>
         <v>-207</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6" t="s">
+        <v>89</v>
+      </c>
+      <c r="G6" t="s">
+        <v>317</v>
+      </c>
+      <c r="H6">
+        <v>207</v>
+      </c>
+      <c r="J6">
+        <v>-207</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>178</v>
       </c>
@@ -32921,8 +33177,20 @@
         <f t="shared" si="0"/>
         <v>-202.8</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7" t="s">
+        <v>178</v>
+      </c>
+      <c r="G7" t="s">
+        <v>318</v>
+      </c>
+      <c r="H7">
+        <v>202.8</v>
+      </c>
+      <c r="J7">
+        <v>-202.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>105</v>
       </c>
@@ -32940,7 +33208,7 @@
         <v>-503.99999999999994</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>55</v>
       </c>
@@ -32957,8 +33225,20 @@
         <f t="shared" si="0"/>
         <v>-204</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9" t="s">
+        <v>55</v>
+      </c>
+      <c r="G9" t="s">
+        <v>320</v>
+      </c>
+      <c r="H9">
+        <v>91.8</v>
+      </c>
+      <c r="J9">
+        <v>-91.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>129</v>
       </c>
@@ -32975,8 +33255,20 @@
         <f t="shared" si="0"/>
         <v>-204.00000000000003</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10" t="s">
+        <v>129</v>
+      </c>
+      <c r="G10" t="s">
+        <v>321</v>
+      </c>
+      <c r="H10">
+        <v>71.400000000000006</v>
+      </c>
+      <c r="J10">
+        <v>-71.400000000000006</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>57</v>
       </c>
@@ -32993,8 +33285,20 @@
         <f t="shared" si="0"/>
         <v>-156</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" t="s">
+        <v>322</v>
+      </c>
+      <c r="H11">
+        <v>70.2</v>
+      </c>
+      <c r="J11">
+        <v>-70.2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>109</v>
       </c>
@@ -33012,7 +33316,7 @@
         <v>-101.99999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>166</v>
       </c>
@@ -33029,8 +33333,20 @@
         <f t="shared" si="0"/>
         <v>-101.99999999999999</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F13" t="s">
+        <v>166</v>
+      </c>
+      <c r="G13" t="s">
+        <v>324</v>
+      </c>
+      <c r="H13">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="J13">
+        <v>-40.799999999999997</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>145</v>
       </c>
@@ -33047,8 +33363,20 @@
         <f t="shared" si="0"/>
         <v>-54</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F14" t="s">
+        <v>145</v>
+      </c>
+      <c r="G14" t="s">
+        <v>325</v>
+      </c>
+      <c r="H14">
+        <v>21.6</v>
+      </c>
+      <c r="J14">
+        <v>-21.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>143</v>
       </c>
@@ -33066,7 +33394,7 @@
         <v>-54</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>164</v>
       </c>
@@ -33083,8 +33411,20 @@
         <f t="shared" si="0"/>
         <v>-54</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F16" t="s">
+        <v>164</v>
+      </c>
+      <c r="G16" t="s">
+        <v>327</v>
+      </c>
+      <c r="H16">
+        <v>21.6</v>
+      </c>
+      <c r="J16">
+        <v>-21.6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>123</v>
       </c>
@@ -33100,6 +33440,18 @@
       <c r="E17">
         <f t="shared" si="0"/>
         <v>-54</v>
+      </c>
+      <c r="F17" t="s">
+        <v>123</v>
+      </c>
+      <c r="G17" t="s">
+        <v>328</v>
+      </c>
+      <c r="H17">
+        <v>21.6</v>
+      </c>
+      <c r="J17">
+        <v>-21.6</v>
       </c>
     </row>
   </sheetData>
